--- a/figures/R3.3_remap_tf_noise_gsea/GSEA_remap_noise.xlsx
+++ b/figures/R3.3_remap_tf_noise_gsea/GSEA_remap_noise.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -415,1204 +415,989 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GO:0032991</t>
+          <t>GO:0005856</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>protein-containing complex</t>
+          <t>cytoskeleton</t>
         </is>
       </c>
       <c r="C2">
-        <v>429</v>
+        <v>69</v>
       </c>
       <c r="D2">
-        <v>0.2162176529113595</v>
+        <v>-0.1694407540093076</v>
       </c>
       <c r="E2">
-        <v>3.486334121843647</v>
+        <v>-1.706511489926708</v>
       </c>
       <c r="F2">
-        <v>4.423099666960354E-09</v>
+        <v>0.01499209166741207</v>
       </c>
       <c r="G2">
-        <v>2.543282308502203E-07</v>
+        <v>0.08413827657748955</v>
       </c>
       <c r="H2">
-        <v>1.885637226440993E-07</v>
+        <v>0.06700256349877887</v>
       </c>
       <c r="I2">
-        <v>342</v>
+        <v>434</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>tags=46%, list=35%, signal=54%</t>
+          <t>tags=62%, list=45%, signal=37%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6872/6908/1385/6667/7528/4149/5460/1869/1025/5978/54880/7469/6829/7936/25942/405/861/1876/4601/865/196528/9441/2078/1874/9757/65980/688/1024/51341/6599/3091/4800/5929/4088/3725/54973/6938/6772/3727/3065/4602/2959/3516/8328/2962/4094/92906/4780/53335/5451/5925/6045/4686/4760/1390/23028/10481/2908/4841/4654/27125/64919/1387/4851/1027/1022/3054/2624/4090/6670/9126/6934/2033/10274/9070/4778/2146/55726/4086/905/23186/4790/6598/6774/5914/23269/6909/25836/4801/467/4297/196/3066/51497/5977/7391/8289/3297/1021/1487/23512/7029/9584/672/9314/6497/54617/5994/466/4605/4089/8932/5885/83860/1052/7764/8085/5469/7421/7004/22936/5093/6929/5970/84844/3183/10856/8243/10725/10589/11091/4802/51230/10614/57504/1050/6928/6886/7520/7494/2353/1406/79718/23309/8861/3662/4205/2623/4609/9968/81608/657/55818/4772/860/8314/132660/5993/7157/2648/10042/26523/6495/56980/5468/8626/3609/80816/2145/2626/7538/7913/22976/10445/56970/6688/9188/4683/9112/29781/9219/4286/3146/11016/4298/3190/221037/6426/571/8473/5927/7027/6777/8535/23135/324/367/1051/5316</t>
+          <t>7756/79692/11083/60436/2101/1499/9611/10735/84307/29855/6907/324/6714/3190/5324/9112/2648/7157/79718/1877/11091/8243/10856/3183/5885/4089/54617/6497/9314/672/9584/7029/1021/3297/5977/5914/10274/9126/10951/2908/5925/4780/1869</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GO:0000785</t>
+          <t>GO:0034708</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>chromatin</t>
+          <t>methyltransferase complex</t>
         </is>
       </c>
       <c r="C3">
-        <v>476</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>0.210945269586101</v>
+        <v>-0.2432758509903516</v>
       </c>
       <c r="E3">
-        <v>3.437105264101282</v>
+        <v>-1.814747423677504</v>
       </c>
       <c r="F3">
-        <v>3.648652418463519E-09</v>
+        <v>0.01889676101685396</v>
       </c>
       <c r="G3">
-        <v>2.543282308502203E-07</v>
+        <v>0.0944838050842698</v>
       </c>
       <c r="H3">
-        <v>1.885637226440993E-07</v>
+        <v>0.07524110793896086</v>
       </c>
       <c r="I3">
-        <v>425</v>
+        <v>209</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>tags=54%, list=44%, signal=59%</t>
+          <t>tags=47%, list=22%, signal=38%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6872/6908/6046/1385/6667/7528/4149/1869/6668/10765/1997/7936/4613/25942/405/861/1876/4601/9682/196528/6671/2078/1874/8019/687/10215/1106/65980/688/8805/2113/6599/3091/4800/4088/4209/3725/6938/1958/10661/6772/3727/3065/5241/3516/4094/4780/53335/5451/5925/6045/4760/1390/23028/10481/2908/5079/4654/27125/64919/1387/2625/10691/3054/4090/6670/10951/9126/6934/8553/2033/10274/9070/4778/2146/4086/27086/4790/6598/6774/4335/5914/23269/546/6909/25836/4801/467/2551/389058/7071/196/3066/11279/6096/5977/2313/7391/8289/3172/3297/9324/3659/6722/79923/23512/26959/7029/23081/7022/2308/7543/93986/9314/23476/54617/7030/466/1316/64843/4089/8932/5885/6935/1052/5469/7421/7004/121340/9889/23435/6929/5970/30009/3183/10856/3200/10725/11091/4802/51230/221937/57504/6945/2002/1050/3110/6928/6886/51548/2353/1406/55145/22882/23309/8861/3662/4205/2623/4609/3660/7544/55818/4772/860/7182/10919/5993/7157/3170/2648/10042/6495/56980/5468/8626/1105/2115/2145/11244/23030/2626/116113/7913/10445/3222/56970/6688/9188/26205/28999/9112/9219/4286/11278/10608/55553/11016/408/3190/79977/221037/571/3215/8473/5927/7027/3169/6777/367/1051/5316/2077/57178/57459/55929/64344/7552/7020/9839/23468/2627/4901/7392/5309/6657/55249/5090/83855/1386/6597/2355/128209/7080/10735/23272/9611/23394/1499/3726/2118/3651/2101/60436/2099/1523/84913/90993/10155/10472/1879/2034/6932/8819/6662/147912</t>
+          <t>51230/11091/10856/8085/23512/3066/4297/23269/2146/9070/3054/6045/5929/9757/1876/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GO:0140513</t>
+          <t>GO:0035097</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nuclear protein-containing complex</t>
+          <t>histone methyltransferase complex</t>
         </is>
       </c>
       <c r="C4">
-        <v>287</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>0.2209152969565146</v>
+        <v>-0.2432758509903516</v>
       </c>
       <c r="E4">
-        <v>3.309110015556196</v>
+        <v>-1.814747423677504</v>
       </c>
       <c r="F4">
-        <v>1.306795739843011E-07</v>
+        <v>0.01889676101685396</v>
       </c>
       <c r="G4">
-        <v>5.00938366939821E-06</v>
+        <v>0.0944838050842698</v>
       </c>
       <c r="H4">
-        <v>3.714051050080138E-06</v>
+        <v>0.07524110793896086</v>
       </c>
       <c r="I4">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>tags=49%, list=35%, signal=46%</t>
+          <t>tags=47%, list=22%, signal=38%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6872/6908/1385/7528/4149/1869/1025/54880/7469/6829/7936/25942/405/861/1876/4601/865/196528/9441/1874/9757/65980/1024/51341/6599/3091/4800/5929/4088/3725/54973/6938/6772/3727/3065/4602/2959/2962/4094/4780/53335/5451/5925/6045/4760/1390/4841/27125/64919/1022/3054/4090/6934/9070/4778/2146/55726/4086/905/23186/4790/6598/6774/5914/23269/25836/4801/467/4297/196/3066/51497/5977/8289/23512/7029/672/54617/5994/466/4605/4089/8932/83860/1052/7764/8085/5469/7421/22936/6929/5970/84844/3183/10856/10589/11091/4802/51230/10614/57504/1050/7520/7494/2353/1406/79718/23309/8861/4609/9968/81608/55818/8314/132660/5993/2648/10042/5468/80816/2145/2626/7913/22976/10445/56970/9188/4683/9112/9219/11016/4298/3190/221037/6426/571/8473/7027/6777/8535/23135/1051</t>
+          <t>51230/11091/10856/8085/23512/3066/4297/23269/2146/9070/3054/6045/5929/9757/1876/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GO:0005667</t>
+          <t>GO:0016514</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>transcription regulator complex</t>
+          <t>SWI/SNF complex</t>
         </is>
       </c>
       <c r="C5">
-        <v>235</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>0.2006776967415339</v>
+        <v>-0.3612059375162823</v>
       </c>
       <c r="E5">
-        <v>2.830404613071827</v>
+        <v>-1.846547262710934</v>
       </c>
       <c r="F5">
-        <v>1.383049623312227E-05</v>
+        <v>0.01422517643897774</v>
       </c>
       <c r="G5">
-        <v>0.000367270334193974</v>
+        <v>0.08413827657748955</v>
       </c>
       <c r="H5">
-        <v>0.0002723011173429007</v>
+        <v>0.06700256349877887</v>
       </c>
       <c r="I5">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>tags=42%, list=28%, signal=40%</t>
+          <t>tags=53%, list=15%, signal=46%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6872/6908/1385/6667/7528/4149/5460/1869/5978/25942/405/861/1876/4601/865/9441/1874/688/3091/4800/4088/3725/6938/6772/3727/3065/4602/2959/3516/8328/2962/4094/4780/5451/5925/4760/1390/23028/10481/4841/4654/1387/1022/2624/4090/6670/6934/2033/4778/4086/23186/4790/6774/5914/6909/4801/467/196/3066/7391/1487/7029/9314/6497/5994/466/4089/8932/83860/1052/5469/7421/7004/6929/5970/10725/10589/4802/57504/1050/6928/6886/7494/2353/1406/79718/8861/4205/2623/4609/4772/860/132660/5993/7157/2648/6495/56980/5468</t>
+          <t>8289/5977/6598/64919/5925/53335/6599/65980/196528</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GO:0090575</t>
+          <t>GO:0032993</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RNA polymerase II transcription regulator complex</t>
+          <t>protein-DNA complex</t>
         </is>
       </c>
       <c r="C6">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>0.2475215995707508</v>
+        <v>-0.245948943153591</v>
       </c>
       <c r="E6">
-        <v>2.743000398799273</v>
+        <v>-1.855632546043184</v>
       </c>
       <c r="F6">
-        <v>1.5968275399738E-05</v>
+        <v>0.01536438094023722</v>
       </c>
       <c r="G6">
-        <v>0.000367270334193974</v>
+        <v>0.08413827657748955</v>
       </c>
       <c r="H6">
-        <v>0.0002723011173429007</v>
+        <v>0.06700256349877887</v>
       </c>
       <c r="I6">
         <v>244</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tags=45%, list=25%, signal=39%</t>
+          <t>tags=51%, list=25%, signal=40%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6872/6908/1385/4149/1869/405/861/1876/4601/865/9441/1874/3091/4800/4088/3725/6938/6772/3727/4602/2959/2962/4094/4780/5451/5925/4760/1390/4841/1022/4090/6934/4778/4086/6774/5914/4801/467/7029/5994/466/4089/83860/1052/5469/7421/6929/10589/4802/1050/7494/2353/1406/8861/4609</t>
+          <t>2623/3662/2353/7520/4802/10856/7004/5469/23512/4801/4778/2033/6934/6670/4780/2959/4800/4149/6667</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GO:0005829</t>
+          <t>GO:0036464</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cytosol</t>
+          <t>cytoplasmic ribonucleoprotein granule</t>
         </is>
       </c>
       <c r="C7">
-        <v>249</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>0.1877544859267556</v>
+        <v>-0.4700944386149003</v>
       </c>
       <c r="E7">
-        <v>2.703560360826115</v>
+        <v>-1.903597354560582</v>
       </c>
       <c r="F7">
-        <v>2.105027466242671E-05</v>
+        <v>0.01324271621020897</v>
       </c>
       <c r="G7">
-        <v>0.0004034635976965119</v>
+        <v>0.08413827657748955</v>
       </c>
       <c r="H7">
-        <v>0.0002991354820450111</v>
+        <v>0.06700256349877887</v>
       </c>
       <c r="I7">
-        <v>432</v>
+        <v>517</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>tags=57%, list=45%, signal=43%</t>
+          <t>tags=100%, list=54%, signal=47%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5460/5978/7469/10765/4601/9682/6671/2078/687/4899/8805/3091/4088/54973/6772/3065/4602/5241/4780/53335/5925/4686/2908/1387/4851/1027/140690/1022/5371/4090/6670/9126/2033/10274/4086/905/4790/6774/5914/25836/4297/196/11279/5977/2313/3297/1021/9324/3659/7022/2308/9314/54617/7030/1316/4605/4089/8932/5885/6935/7421/5093/5970/3183/10856/8243/10725/51230/6945/3110/7541/7520/7494/2353/22882/3662/4205/3660/81608/4772/860/8314/7728/7157/1820/26523/5468/3609/49854/7706/7538/9188/26205/4683/9112/5324/4286/2521/11278/84232/4298/408/6714/7775/571/7026/3215/8473/7027/6777/324/367/2077/57178/7750/3096/55929/64344/9839/57591/602/4901/8531/6657/2122/84307/7025/10735/55893/9611/1499/3651/5948/2099/1523/90993/51523/2034/147912/90850/79692/79753/9575</t>
+          <t>2553/9575/3190/7538/7706/26523/64332/23435/5093/1025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GO:0005737</t>
+          <t>GO:0035770</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cytoplasm</t>
+          <t>ribonucleoprotein granule</t>
         </is>
       </c>
       <c r="C8">
-        <v>424</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>0.1650151564564988</v>
+        <v>-0.4710830704521556</v>
       </c>
       <c r="E8">
-        <v>2.65567825499761</v>
+        <v>-2.09141312499695</v>
       </c>
       <c r="F8">
-        <v>6.758465192331272E-05</v>
+        <v>0.003576926588493112</v>
       </c>
       <c r="G8">
-        <v>0.0009715293713976203</v>
+        <v>0.02570915985479424</v>
       </c>
       <c r="H8">
-        <v>0.0007203101060247804</v>
+        <v>0.02047319823676979</v>
       </c>
       <c r="I8">
-        <v>346</v>
+        <v>517</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>tags=44%, list=36%, signal=50%</t>
+          <t>tags=100%, list=54%, signal=47%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6908/6046/6667/5460/1869/1025/5978/7469/10765/405/4601/9682/6671/2078/1874/687/4899/10215/688/51341/8805/2113/6599/3091/4088/4209/54973/6938/1958/6772/3065/4602/5241/3516/4094/4780/53335/5451/5925/6045/4686/4760/604/1390/2908/4654/1387/4851/1027/140690/80319/10691/55734/1022/5371/3054/2624/4090/6670/9126/8553/2033/10274/4778/55726/4086/905/4790/6774/5914/6909/25836/4297/196/3066/11279/5977/2313/7391/3172/3297/1021/9324/3659/1487/6722/7022/2308/672/9314/6497/54617/7030/1316/4605/4089/8932/5885/6935/7764/7421/7004/121340/5093/9889/23435/6929/5970/3183/10856/8243/10725/51230/221937/10614/57504/6945/2002/3110/7541/7520/51548/64332/1877/7494/2353/22882/23309/3662/4205/84662/4609/3660/81608/55818/4772/860/8314/7728/7157/3170/2648/1820/26523/6495/8148/5468/8626/1105/3609/49854/7706/7538/7913/10445/9188/26205/4683/9112/5324/4286/2521/11278/84232/55553/3146/11016/4298/408/3190/6714/7775/6426/571/7026/3215/8473/7027/6777/324/367/1051/5316/2077/57178/7750/3096</t>
+          <t>3191/2553/9575/3190/7538/7706/26523/64332/23435/5093/3297/1025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO:1902494</t>
+          <t>GO:1990234</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>catalytic complex</t>
+          <t>transferase complex</t>
         </is>
       </c>
       <c r="C9">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="D9">
-        <v>0.2175973166497941</v>
+        <v>-0.1981038861468934</v>
       </c>
       <c r="E9">
-        <v>2.607247191928534</v>
+        <v>-2.160269231116381</v>
       </c>
       <c r="F9">
-        <v>3.488967883472846E-05</v>
+        <v>0.004850524774398883</v>
       </c>
       <c r="G9">
-        <v>0.0005731875808562532</v>
+        <v>0.03281237347387479</v>
       </c>
       <c r="H9">
-        <v>0.0004249720279117302</v>
+        <v>0.02612976194258222</v>
       </c>
       <c r="I9">
-        <v>398</v>
+        <v>209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>tags=58%, list=41%, signal=40%</t>
+          <t>tags=42%, list=22%, signal=36%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6872/6908/7528/4149/1025/54880/25942/1876/196528/9757/65980/1024/51341/6599/5929/3065/2959/2962/53335/5925/6045/23028/64919/1387/1027/1022/3054/2033/9070/2146/905/23186/6598/23269/4297/3066/5977/8289/1021/23512/672/54617/8932/83860/7764/8085/5469/3183/10856/11091/51230/57504/7520/79718/23309/9968/55818/2648/10042/26523/2145/7913/22976/10445/56970/9188/9112/9219/3190/221037/6426/8473/8535/23135/324/57459/55929/6907/23468/55249/2122/7307/1386/6597/9611/1499</t>
+          <t>51230/11091/10856/5469/8085/83860/672/23512/1021/3066/4297/23269/905/2146/9070/2033/3054/1022/1027/1387/6045/5925/2962/2959/5929/51341/1024/9757/1876/54880/1025/4149/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:0044665</t>
+          <t>GO:0061695</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MLL1/2 complex</t>
+          <t>transferase complex, transferring phosphorus-containing groups</t>
         </is>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>0.4920667750328854</v>
+        <v>-0.370576864866505</v>
       </c>
       <c r="E10">
-        <v>2.484350457552466</v>
+        <v>-2.203271392255046</v>
       </c>
       <c r="F10">
-        <v>0.0001584663858794727</v>
+        <v>0.001750055033476567</v>
       </c>
       <c r="G10">
-        <v>0.002024848264015484</v>
+        <v>0.01341708858998701</v>
       </c>
       <c r="H10">
-        <v>0.001501260497805531</v>
+        <v>0.01068454652017272</v>
       </c>
       <c r="I10">
-        <v>208</v>
+        <v>299</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>tags=68%, list=22%, signal=55%</t>
+          <t>tags=70%, list=31%, signal=49%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6872/4149/1876/9757/5929/6045/3054/9070/23269/4297/10856/11091/51230</t>
+          <t>56970/2648/9968/7520/83860/1021/905/1022/5925/2962/2959/51341/1024/1025/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO:0000791</t>
+          <t>GO:0099080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>euchromatin</t>
+          <t>supramolecular complex</t>
         </is>
       </c>
       <c r="C11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D11">
-        <v>0.4332474233854748</v>
+        <v>-0.2977691607928926</v>
       </c>
       <c r="E11">
-        <v>2.366770773590142</v>
+        <v>-2.246605083520115</v>
       </c>
       <c r="F11">
-        <v>0.0002803990864477733</v>
+        <v>0.001633792763539584</v>
       </c>
       <c r="G11">
-        <v>0.003224589494149393</v>
+        <v>0.01341708858998701</v>
       </c>
       <c r="H11">
-        <v>0.002390771158133647</v>
+        <v>0.01068454652017272</v>
       </c>
       <c r="I11">
-        <v>201</v>
+        <v>441</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>tags=61%, list=21%, signal=49%</t>
+          <t>tags=76%, list=46%, signal=43%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6908/1385/6667/8805/3091/3725/6045/4654/27125/9070/3297/9314/6929/10856</t>
+          <t>2553/7756/9575/1499/6597/23468/324/6714/3190/9112/7913/7538/7706/26523/92822/64332/8243/23435/5093/54617/3297/6598/4654/2959/6599/196528/25942/1025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO:0071339</t>
+          <t>GO:1902554</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MLL1 complex</t>
+          <t>serine/threonine protein kinase complex</t>
         </is>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>0.4738552908080838</v>
+        <v>-0.5568722512601556</v>
       </c>
       <c r="E12">
-        <v>2.326976965352737</v>
+        <v>-2.254994863267092</v>
       </c>
       <c r="F12">
-        <v>0.0007284040173621147</v>
+        <v>0.001567094756395386</v>
       </c>
       <c r="G12">
-        <v>0.005983318714045941</v>
+        <v>0.01341708858998701</v>
       </c>
       <c r="H12">
-        <v>0.00443614476739333</v>
+        <v>0.01068454652017272</v>
       </c>
       <c r="I12">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>tags=67%, list=22%, signal=53%</t>
+          <t>tags=82%, list=26%, signal=62%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6872/4149/1876/5929/6045/3054/9070/23269/4297/10856/11091/51230</t>
+          <t>9968/7520/1021/905/1022/5925/51341/1024/1025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GO:1990234</t>
+          <t>GO:1902911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>transferase complex</t>
+          <t>protein kinase complex</t>
         </is>
       </c>
       <c r="C13">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>0.2429596679727249</v>
+        <v>-0.5568722512601556</v>
       </c>
       <c r="E13">
-        <v>2.291522579374802</v>
+        <v>-2.254994863267092</v>
       </c>
       <c r="F13">
-        <v>0.00111991814846608</v>
+        <v>0.001567094756395386</v>
       </c>
       <c r="G13">
-        <v>0.008586039138239944</v>
+        <v>0.01341708858998701</v>
       </c>
       <c r="H13">
-        <v>0.00636585052812298</v>
+        <v>0.01068454652017272</v>
       </c>
       <c r="I13">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>tags=42%, list=22%, signal=36%</t>
+          <t>tags=82%, list=26%, signal=62%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6872/6908/4149/1025/54880/1876/9757/1024/51341/5929/2959/2962/5925/6045/1387/1027/1022/3054/2033/9070/2146/905/23269/4297/3066/1021/23512/672/83860/8085/5469/10856/11091/51230</t>
+          <t>9968/7520/1021/905/1022/5925/51341/1024/1025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO:1902554</t>
+          <t>GO:0000791</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>serine/threonine protein kinase complex</t>
+          <t>euchromatin</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>0.5810410518660372</v>
+        <v>-0.3808713614105275</v>
       </c>
       <c r="E14">
-        <v>2.28288084232791</v>
+        <v>-2.264477505975296</v>
       </c>
       <c r="F14">
-        <v>0.0006475169789941582</v>
+        <v>0.001162949997651638</v>
       </c>
       <c r="G14">
-        <v>0.005983318714045941</v>
+        <v>0.01215811361181258</v>
       </c>
       <c r="H14">
-        <v>0.00443614476739333</v>
+        <v>0.009681976057004067</v>
       </c>
       <c r="I14">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>tags=82%, list=25%, signal=62%</t>
+          <t>tags=61%, list=21%, signal=49%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1025/1024/51341/5925/1022/905/1021/7520/9968</t>
+          <t>10856/6929/9314/3297/9070/27125/4654/6045/3725/3091/8805/6667/1385/6908</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GO:1902911</t>
+          <t>GO:0071339</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>protein kinase complex</t>
+          <t>MLL1 complex</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>0.5810410518660372</v>
+        <v>-0.440968698762612</v>
       </c>
       <c r="E15">
-        <v>2.28288084232791</v>
+        <v>-2.30863671650667</v>
       </c>
       <c r="F15">
-        <v>0.0006475169789941582</v>
+        <v>0.000908910261447357</v>
       </c>
       <c r="G15">
-        <v>0.005983318714045941</v>
+        <v>0.01045246800664461</v>
       </c>
       <c r="H15">
-        <v>0.00443614476739333</v>
+        <v>0.008323704499570532</v>
       </c>
       <c r="I15">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>tags=82%, list=25%, signal=62%</t>
+          <t>tags=67%, list=22%, signal=53%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1025/1024/51341/5925/1022/905/1021/7520/9968</t>
+          <t>51230/11091/10856/4297/23269/9070/3054/6045/5929/1876/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GO:0061695</t>
+          <t>GO:0044665</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>transferase complex, transferring phosphorus-containing groups</t>
+          <t>MLL1/2 complex</t>
         </is>
       </c>
       <c r="C16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>0.4161176238283834</v>
+        <v>-0.459490693037087</v>
       </c>
       <c r="E16">
-        <v>2.273193046959072</v>
+        <v>-2.445867136667184</v>
       </c>
       <c r="F16">
-        <v>0.0007224232964019329</v>
+        <v>0.0004544790395210988</v>
       </c>
       <c r="G16">
-        <v>0.005983318714045941</v>
+        <v>0.005807232171658486</v>
       </c>
       <c r="H16">
-        <v>0.00443614476739333</v>
+        <v>0.004624523560039251</v>
       </c>
       <c r="I16">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>tags=70%, list=31%, signal=49%</t>
+          <t>tags=68%, list=22%, signal=55%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6872/6908/1025/1024/51341/2959/2962/5925/1022/905/1021/83860/7520/9968/2648/56970</t>
+          <t>51230/11091/10856/4297/23269/9070/3054/6045/5929/9757/1876/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO:0099080</t>
+          <t>GO:0005737</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>supramolecular complex</t>
+          <t>cytoplasm</t>
         </is>
       </c>
       <c r="C17">
-        <v>37</v>
+        <v>424</v>
       </c>
       <c r="D17">
-        <v>0.32411414618955</v>
+        <v>-0.1246803923357143</v>
       </c>
       <c r="E17">
-        <v>2.17000122330999</v>
+        <v>-2.48921492355484</v>
       </c>
       <c r="F17">
-        <v>0.001795944412916958</v>
+        <v>0.0002086378167135866</v>
       </c>
       <c r="G17">
-        <v>0.01290835046784064</v>
+        <v>0.002999168615257808</v>
       </c>
       <c r="H17">
-        <v>0.009570493253044316</v>
+        <v>0.002388353954484479</v>
       </c>
       <c r="I17">
-        <v>440</v>
+        <v>347</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>tags=76%, list=46%, signal=43%</t>
+          <t>tags=44%, list=36%, signal=50%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1025/25942/196528/6599/2959/4654/6598/3297/54617/5093/23435/8243/64332/92822/26523/7706/7538/7913/9112/3190/6714/324/23468/6597/1499/9575/7756/2553</t>
+          <t>3096/7750/57178/2077/5316/1051/367/324/6777/7027/8473/3215/7026/571/6426/7775/6714/3190/408/4298/11016/3146/55553/84232/11278/2521/4286/5324/9112/4683/26205/9188/10445/7913/7538/7706/49854/3609/1105/8626/5468/8148/6495/26523/1820/2648/3170/7157/7728/8314/860/4772/55818/81608/3660/4609/84662/4205/3662/23309/22882/2353/7494/1877/64332/51548/7520/7541/3110/2002/6945/57504/10614/221937/51230/10725/8243/10856/3183/5970/6929/23435/9889/5093/121340/7004/7421/7764/6935/5885/8932/4089/4605/1316/7030/54617/6497/9314/672/2308/7022/6722/1487/3659/9324/1021/3297/3172/7391/2313/5977/11279/3066/196/4297/25836/6909/5914/6774/4790/905/4086/55726/4778/10274/2033/8553/9126/6670/4090/2624/3054/5371/1022/55734/10691/80319/140690/1027/4851/1387/4654/2908/1390/604/4760/4686/6045/5925/5451/53335/4780/4094/3516/5241/4602/3065/6772/1958/6938/54973/4209/4088/3091/6599/2113/8805/51341/688/10215/4899/687/1874/2078/6671/9682/4601/405/10765/7469/5978/1025/1869/5460/6667/6046/6908</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GO:0035770</t>
+          <t>GO:1902494</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ribonucleoprotein granule</t>
+          <t>catalytic complex</t>
         </is>
       </c>
       <c r="C18">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D18">
-        <v>0.4710830704521556</v>
+        <v>-0.1758842561870777</v>
       </c>
       <c r="E18">
-        <v>2.026427734280372</v>
+        <v>-2.582359194989498</v>
       </c>
       <c r="F18">
-        <v>0.004305676369779118</v>
+        <v>0.0001711296282795975</v>
       </c>
       <c r="G18">
-        <v>0.02912663426615286</v>
+        <v>0.002811415321736244</v>
       </c>
       <c r="H18">
-        <v>0.02159503318588908</v>
+        <v>0.002238838745913531</v>
       </c>
       <c r="I18">
-        <v>516</v>
+        <v>399</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>tags=100%, list=54%, signal=47%</t>
+          <t>tags=58%, list=41%, signal=40%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1025/3297/5093/23435/64332/26523/7706/7538/3190/9575/2553/3191/7150</t>
+          <t>1499/9611/6597/1386/7307/2122/55249/23468/6907/55929/57459/324/23135/8535/8473/6426/221037/3190/9219/9112/9188/56970/10445/22976/7913/2145/26523/10042/2648/55818/9968/23309/79718/7520/57504/51230/11091/10856/3183/5469/8085/7764/83860/8932/54617/672/23512/1021/8289/5977/3066/4297/23269/6598/23186/905/2146/9070/2033/3054/1022/1027/1387/64919/23028/6045/5925/53335/2962/2959/3065/5929/6599/51341/1024/65980/9757/196528/1876/25942/54880/1025/4149/7528/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GO:0016514</t>
+          <t>GO:0005829</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SWI/SNF complex</t>
+          <t>cytosol</t>
         </is>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>249</v>
       </c>
       <c r="D19">
-        <v>0.4095395339885844</v>
+        <v>-0.1490103202958628</v>
       </c>
       <c r="E19">
-        <v>1.970260748668736</v>
+        <v>-2.617070737131445</v>
       </c>
       <c r="F19">
-        <v>0.004884815993037416</v>
+        <v>0.000170351711650198</v>
       </c>
       <c r="G19">
-        <v>0.03120854662218349</v>
+        <v>0.002811415321736244</v>
       </c>
       <c r="H19">
-        <v>0.0231386020722825</v>
+        <v>0.002238838745913531</v>
       </c>
       <c r="I19">
-        <v>143</v>
+        <v>433</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>tags=53%, list=15%, signal=46%</t>
+          <t>tags=57%, list=45%, signal=43%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>196528/65980/6599/53335/5925/64919/6598/5977/8289</t>
+          <t>9575/79753/79692/90850/147912/2034/51523/90993/1523/2099/5948/3651/1499/9611/55893/10735/7025/84307/2122/6657/8531/4901/602/57591/9839/64344/55929/3096/7750/57178/2077/367/324/6777/7027/8473/3215/7026/571/7775/6714/408/4298/84232/11278/2521/4286/5324/9112/4683/26205/9188/7538/7706/49854/3609/5468/26523/1820/7157/7728/8314/860/4772/81608/3660/4205/3662/22882/2353/7494/7520/7541/3110/6945/51230/10725/8243/10856/3183/5970/5093/7421/6935/5885/8932/4089/4605/1316/7030/54617/9314/2308/7022/3659/9324/1021/3297/2313/5977/11279/196/4297/25836/5914/6774/4790/905/4086/10274/2033/9126/6670/4090/5371/1022/140690/1027/4851/1387/2908/4686/5925/53335/4780/5241/4602/3065/6772/54973/4088/3091/8805/4899/687/2078/6671/9682/4601/10765/7469/5978/5460</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GO:0032993</t>
+          <t>GO:0090575</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>protein-DNA complex</t>
+          <t>RNA polymerase II transcription regulator complex</t>
         </is>
       </c>
       <c r="C20">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="D20">
-        <v>0.2933641909836252</v>
+        <v>-0.2006495082610016</v>
       </c>
       <c r="E20">
-        <v>1.964124864014767</v>
+        <v>-2.727381413845893</v>
       </c>
       <c r="F20">
-        <v>0.006311197125754513</v>
+        <v>0.0001428524309473976</v>
       </c>
       <c r="G20">
-        <v>0.03819935102430363</v>
+        <v>0.002811415321736244</v>
       </c>
       <c r="H20">
-        <v>0.02832171563357981</v>
+        <v>0.002238838745913531</v>
       </c>
       <c r="I20">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>tags=51%, list=25%, signal=40%</t>
+          <t>tags=45%, list=25%, signal=38%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6667/4149/4800/2959/4780/6670/6934/2033/4778/4801/23512/5469/7004/10856/4802/7520/2353/3662/2623</t>
+          <t>4609/8861/1406/2353/7494/1050/4802/10589/6929/7421/5469/1052/83860/4089/466/5994/7029/467/4801/5914/6774/4086/4778/6934/4090/1022/4841/1390/4760/5925/5451/4780/4094/2962/2959/4602/3727/6772/6938/3725/4088/4800/3091/1874/9441/865/4601/1876/861/405/1869/4149/1385/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GO:0034708</t>
+          <t>GO:0005667</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>methyltransferase complex</t>
+          <t>transcription regulator complex</t>
         </is>
       </c>
       <c r="C21">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="D21">
-        <v>0.2852082650945477</v>
+        <v>-0.1577912648076182</v>
       </c>
       <c r="E21">
-        <v>1.885905728653465</v>
+        <v>-2.739366750676907</v>
       </c>
       <c r="F21">
-        <v>0.008064931784146552</v>
+        <v>3.339003307208809E-05</v>
       </c>
       <c r="G21">
-        <v>0.04416510262746921</v>
+        <v>0.0009599634508225327</v>
       </c>
       <c r="H21">
-        <v>0.03274483581533186</v>
+        <v>0.0007644560203346485</v>
       </c>
       <c r="I21">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>tags=47%, list=22%, signal=38%</t>
+          <t>tags=42%, list=29%, signal=40%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6872/4149/1876/9757/5929/6045/3054/9070/2146/23269/4297/3066/23512/8085/10856/11091/51230</t>
+          <t>5468/56980/6495/2648/7157/5993/132660/860/4772/4609/2623/4205/8861/79718/1406/2353/7494/6886/6928/1050/57504/4802/10589/10725/5970/6929/7004/7421/5469/1052/83860/8932/4089/466/5994/6497/9314/7029/1487/7391/3066/196/467/4801/6909/5914/6774/4790/23186/4086/4778/2033/6934/6670/4090/2624/1022/1387/4654/4841/10481/23028/1390/4760/5925/5451/4780/4094/2962/8328/3516/2959/4602/3065/3727/6772/6938/3725/4088/4800/3091/688/1874/9441/865/4601/1876/861/405/25942/5978/1869/5460/4149/7528/6667/1385/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GO:0035097</t>
+          <t>GO:0140513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>histone methyltransferase complex</t>
+          <t>nuclear protein-containing complex</t>
         </is>
       </c>
       <c r="C22">
-        <v>36</v>
+        <v>287</v>
       </c>
       <c r="D22">
-        <v>0.2852082650945477</v>
+        <v>-0.1766257608121525</v>
       </c>
       <c r="E22">
-        <v>1.885905728653465</v>
+        <v>-3.248530395263305</v>
       </c>
       <c r="F22">
-        <v>0.008064931784146552</v>
+        <v>4.097012559283651E-07</v>
       </c>
       <c r="G22">
-        <v>0.04416510262746921</v>
+        <v>1.570521481058733E-05</v>
       </c>
       <c r="H22">
-        <v>0.03274483581533186</v>
+        <v>1.250666991781325E-05</v>
       </c>
       <c r="I22">
-        <v>208</v>
+        <v>342</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>tags=47%, list=22%, signal=38%</t>
+          <t>tags=49%, list=35%, signal=45%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6872/4149/1876/9757/5929/6045/3054/9070/2146/23269/4297/3066/23512/8085/10856/11091/51230</t>
+          <t>1051/23135/8535/6777/7027/8473/571/6426/221037/3190/4298/11016/9219/9112/4683/9188/56970/10445/22976/7913/2626/2145/80816/5468/10042/2648/5993/132660/8314/55818/81608/9968/4609/8861/23309/79718/1406/2353/7494/7520/1050/57504/10614/51230/4802/11091/10589/10856/3183/84844/5970/6929/22936/7421/5469/8085/7764/1052/83860/8932/4089/4605/466/5994/54617/672/7029/23512/8289/5977/51497/3066/196/4297/467/4801/25836/23269/5914/6774/6598/4790/23186/905/4086/55726/2146/4778/9070/6934/4090/3054/1022/64919/27125/4841/1390/4760/6045/5925/5451/53335/4780/4094/2962/2959/4602/3065/3727/6772/6938/54973/3725/4088/5929/4800/3091/6599/51341/1024/65980/9757/1874/9441/196528/865/4601/1876/861/405/25942/7936/6829/7469/54880/1025/1869/4149/7528/1385/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GO:0036464</t>
+          <t>GO:0000785</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cytoplasmic ribonucleoprotein granule</t>
+          <t>chromatin</t>
         </is>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>476</v>
       </c>
       <c r="D23">
-        <v>0.4700944386149003</v>
+        <v>-0.1683054408510895</v>
       </c>
       <c r="E23">
-        <v>1.846977222267379</v>
+        <v>-3.337089085658244</v>
       </c>
       <c r="F23">
-        <v>0.01218166516535223</v>
+        <v>2.203374326208636E-07</v>
       </c>
       <c r="G23">
-        <v>0.06090832582676116</v>
+        <v>1.266940237569966E-05</v>
       </c>
       <c r="H23">
-        <v>0.04515857567018448</v>
+        <v>1.008913507263954E-05</v>
       </c>
       <c r="I23">
-        <v>516</v>
+        <v>426</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>tags=100%, list=54%, signal=47%</t>
+          <t>tags=54%, list=44%, signal=59%</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1025/5093/23435/64332/26523/7706/7538/3190/9575/2553/7150</t>
+          <t>147912/6662/8819/6932/2034/1879/10472/10155/90993/84913/1523/2099/60436/2101/3651/2118/3726/1499/23394/9611/23272/10735/7080/128209/2355/6597/1386/83855/5090/55249/6657/5309/7392/4901/2627/23468/9839/7020/7552/64344/55929/57459/57178/2077/5316/1051/367/6777/3169/7027/5927/8473/3215/571/221037/79977/3190/408/11016/55553/10608/11278/4286/9219/9112/28999/26205/9188/6688/56970/3222/10445/7913/116113/2626/23030/11244/2145/2115/1105/8626/5468/56980/6495/10042/2648/3170/7157/5993/10919/7182/860/4772/55818/7544/3660/4609/2623/4205/3662/8861/23309/22882/55145/1406/2353/51548/6886/6928/3110/1050/2002/6945/57504/221937/51230/4802/11091/10725/3200/10856/3183/30009/5970/6929/23435/9889/121340/7004/7421/5469/1052/6935/5885/8932/4089/64843/1316/466/7030/54617/23476/9314/93986/7543/2308/7022/23081/7029/26959/23512/79923/6722/3659/9324/3297/3172/8289/7391/2313/5977/6096/11279/3066/196/7071/389058/2551/467/4801/25836/6909/546/23269/5914/4335/6774/6598/4790/27086/4086/2146/4778/9070/10274/2033/8553/6934/9126/10951/6670/4090/3054/10691/2625/1387/64919/27125/4654/5079/2908/10481/23028/1390/4760/6045/5925/5451/53335/4780/4094/3516/5241/3065/3727/6772/10661/1958/6938/3725/4209/4088/4800/3091/6599/2113/8805/688/65980/1106/10215/687/8019/1874/2078/6671/196528/9682/4601/1876/861/405/25942/4613/7936/1997/10765/6668/1869/4149/7528/6667/1385/6046/6908/6872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GO:0140535</t>
+          <t>GO:0032991</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>intracellular protein-containing complex</t>
+          <t>protein-containing complex</t>
         </is>
       </c>
       <c r="C24">
-        <v>63</v>
+        <v>429</v>
       </c>
       <c r="D24">
-        <v>0.214570909831699</v>
+        <v>-0.1730849465578376</v>
       </c>
       <c r="E24">
-        <v>1.811761165199779</v>
+        <v>-3.464610230308045</v>
       </c>
       <c r="F24">
-        <v>0.01618297815939569</v>
+        <v>6.240493959311298E-08</v>
       </c>
       <c r="G24">
-        <v>0.07157855724348093</v>
+        <v>7.176568053207993E-06</v>
       </c>
       <c r="H24">
-        <v>0.05306968546198586</v>
+        <v>5.714978678527189E-06</v>
       </c>
       <c r="I24">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>tags=56%, list=37%, signal=37%</t>
+          <t>tags=46%, list=36%, signal=54%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6872/6908/54880/405/1024/2959/2962/6045/4686/1387/1027/1022/3054/2033/4790/196/3297/672/83860/5469/10856/11091/51230/7520/9968/2648/26523/7538/10445/56970/8473/8535/324/55929/602</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>GO:0005856</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cytoskeleton</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>69</v>
-      </c>
-      <c r="D25">
-        <v>0.2023872969456758</v>
-      </c>
-      <c r="E25">
-        <v>1.778993284000087</v>
-      </c>
-      <c r="F25">
-        <v>0.01216422756853742</v>
-      </c>
-      <c r="G25">
-        <v>0.06090832582676116</v>
-      </c>
-      <c r="H25">
-        <v>0.04515857567018448</v>
-      </c>
-      <c r="I25">
-        <v>433</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>tags=62%, list=45%, signal=37%</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1869/4780/5925/2908/10951/9126/10274/5914/5977/3297/1021/7029/9584/672/9314/6497/54617/4089/5885/3183/10856/8243/11091/1877/79718/7157/2648/9112/5324/3190/6714/324/6907/29855/84307/10735/9611/1499/2101/60436/11083/79692/7756</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>GO:0015630</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>microtubule cytoskeleton</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>62</v>
-      </c>
-      <c r="D26">
-        <v>0.2068606550511703</v>
-      </c>
-      <c r="E26">
-        <v>1.750366354957464</v>
-      </c>
-      <c r="F26">
-        <v>0.01992536783167659</v>
-      </c>
-      <c r="G26">
-        <v>0.08486730743121511</v>
-      </c>
-      <c r="H26">
-        <v>0.06292221420529449</v>
-      </c>
-      <c r="I26">
-        <v>433</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>tags=63%, list=45%, signal=37%</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>1869/4780/5925/2908/10951/9126/10274/5977/3297/1021/7029/9584/672/9314/6497/54617/4089/5885/10856/8243/11091/1877/79718/7157/2648/9112/5324/324/6907/29855/84307/10735/9611/1499/2101/60436/11083/79692/7756</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>GO:0070603</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SWI/SNF superfamily-type complex</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>44</v>
-      </c>
-      <c r="D27">
-        <v>0.2399035483823343</v>
-      </c>
-      <c r="E27">
-        <v>1.711028476391466</v>
-      </c>
-      <c r="F27">
-        <v>0.01551400780356582</v>
-      </c>
-      <c r="G27">
-        <v>0.07136443589640278</v>
-      </c>
-      <c r="H27">
-        <v>0.05291093187742449</v>
-      </c>
-      <c r="I27">
-        <v>386</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>tags=61%, list=40%, signal=39%</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>7528/196528/65980/6599/3065/53335/5925/64919/6598/3066/5977/8289/23512/54617/8932/10856/57504/10042/7913/10445/9188/9112/9219/57459/55929/55249/6597</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>GO:1904949</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ATPase complex</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>44</v>
-      </c>
-      <c r="D28">
-        <v>0.2399035483823343</v>
-      </c>
-      <c r="E28">
-        <v>1.711028476391466</v>
-      </c>
-      <c r="F28">
-        <v>0.01551400780356582</v>
-      </c>
-      <c r="G28">
-        <v>0.07136443589640278</v>
-      </c>
-      <c r="H28">
-        <v>0.05291093187742449</v>
-      </c>
-      <c r="I28">
-        <v>386</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>tags=61%, list=40%, signal=39%</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>7528/196528/65980/6599/3065/53335/5925/64919/6598/3066/5977/8289/23512/54617/8932/10856/57504/10042/7913/10445/9188/9112/9219/57459/55929/55249/6597</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GO:0000775</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>chromosome, centromeric region</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>36</v>
-      </c>
-      <c r="D29">
-        <v>0.2555282911022614</v>
-      </c>
-      <c r="E29">
-        <v>1.689650430933453</v>
-      </c>
-      <c r="F29">
-        <v>0.02269321952242954</v>
-      </c>
-      <c r="G29">
-        <v>0.09320429446712133</v>
-      </c>
-      <c r="H29">
-        <v>0.06910341283145839</v>
-      </c>
-      <c r="I29">
-        <v>236</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>tags=47%, list=24%, signal=37%</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>25942/9682/196528/6599/2959/10951/9126/10274/2146/6598/546/3297/23081/5885/8243/51548/92822</t>
+          <t>5316/1051/367/324/23135/8535/6777/7027/5927/8473/571/6426/221037/3190/4298/11016/3146/4286/9219/29781/9112/4683/9188/6688/56970/10445/22976/7913/7538/2626/2145/80816/3609/8626/5468/56980/6495/26523/10042/2648/7157/5993/132660/8314/860/4772/55818/657/81608/9968/4609/2623/4205/3662/8861/23309/79718/1406/2353/7494/7520/6886/6928/1050/57504/10614/51230/4802/11091/10589/10725/8243/10856/3183/84844/5970/6929/5093/22936/7004/7421/5469/8085/7764/1052/83860/5885/8932/4089/4605/466/5994/54617/6497/9314/672/9584/7029/23512/1487/1021/3297/8289/7391/5977/51497/3066/196/4297/467/4801/25836/6909/23269/5914/6774/6598/4790/23186/905/4086/55726/2146/4778/9070/10274/2033/6934/9126/6670/4090/2624/3054/1022/1027/4851/1387/64919/27125/4654/4841/2908/10481/23028/1390/4760/4686/6045/5925/5451/53335/4780/92906/4094/2962/8328/3516/2959/4602/3065/3727/6772/6938/54973/3725/4088/5929/4800/3091/6599/51341/1024/688/65980/9757/1874/2078/9441/196528/865/4601/1876/861/405/25942/7936/6829/7469/54880/5978/1025/1869/5460/4149/7528/6667/1385/6908/6872</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1686,817 +1471,473 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GO:1902494</t>
+          <t>GO:0000791</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>catalytic complex</t>
+          <t>euchromatin</t>
         </is>
       </c>
       <c r="C2">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>0.2103218630155897</v>
+        <v>-0.3273262666103552</v>
       </c>
       <c r="E2">
-        <v>2.593489783445196</v>
+        <v>-1.888521650937372</v>
       </c>
       <c r="F2">
-        <v>4.48590486816003E-05</v>
+        <v>0.006286580303872253</v>
       </c>
       <c r="G2">
-        <v>0.005158790598384035</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H2">
-        <v>0.004155364509453502</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I2">
-        <v>592</v>
+        <v>223</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>tags=78%, list=61%, signal=36%</t>
+          <t>tags=57%, list=23%, signal=45%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>54880/6872/1025/51341/4149/3065/25942/3183/7528/196528/8535/5929/9757/6599/11091/1876/6908/54617/8289/1024/4297/6598/11143/23028/6045/65980/1027/23135/26147/6597/3054/5925/55818/9070/1387/2962/905/26523/3190/83860/2033/5977/55929/2959/54815/53335/9112/10042/64919/5469/7764/10856/3066/8085/1021/57459/23512/51230/3720/63925/1022/56970/10445/2146/29117/22976/221037/8467/79718/57492/8932/22823/324/57504/672/1655/23186/5926/6760/7703/23269/8819/55696/6426/53615/2122/9611/1499/23309/6907/84759/23492/10013/54623/7520/23468/7913/4221/7307/2145/6605/3187/51317/5928/58508/9188/1457/57680/6604/8850/5591/8473/8607/55249/29998/9219</t>
+          <t>10856/6929/9314/27125/9070/6045/3725/3091/4654/6908/6667/1385/8805</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GO:0140513</t>
+          <t>GO:0044665</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nuclear protein-containing complex</t>
+          <t>MLL1/2 complex</t>
         </is>
       </c>
       <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>-0.3788702584558448</v>
+      </c>
+      <c r="E3">
+        <v>-1.977671227502474</v>
+      </c>
+      <c r="F3">
+        <v>0.005763764541390992</v>
+      </c>
+      <c r="G3">
+        <v>0.07229567349453091</v>
+      </c>
+      <c r="H3">
+        <v>0.06286580303872254</v>
+      </c>
+      <c r="I3">
         <v>287</v>
       </c>
-      <c r="D3">
-        <v>0.1534109197677713</v>
-      </c>
-      <c r="E3">
-        <v>2.346881942272074</v>
-      </c>
-      <c r="F3">
-        <v>0.0003392597970353108</v>
-      </c>
-      <c r="G3">
-        <v>0.01950743832953037</v>
-      </c>
-      <c r="H3">
-        <v>0.01571308533637229</v>
-      </c>
-      <c r="I3">
-        <v>406</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>tags=52%, list=42%, signal=43%</t>
+          <t>tags=68%, list=30%, signal=49%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54880/6872/1025/51341/4149/3065/25942/3183/7528/196528/10614/1869/1385/8535/861/5929/9757/6599/865/11091/4088/7029/7936/4605/1876/4601/6908/1052/54617/8289/3091/1024/4790/405/3725/4297/1874/4841/6829/6598/11143/4609/54973/6045/65980/6772/9441/7469/467/132660/6774/23135/26147/6597/3054/4086/5925/55818/4602/9070/2962/905/3190/27125/10589/83860/3727/55726/6934/5977/4778/1390/55929/5994/2959/466/6929/84844/54815/53335/6938/9112/10042/25836/64919/5469/7764/10856/5914/3066/8085/4800/51497/6256/57459/4760/571/4090/23512/6932/5451/51230/3720/4801/81608/63925/1022/5970/56970/10445/4802/5468/2146/29117/1050/11335/22976/4780/2309/55120/221037/8467/4094/4089/79718/196/10155/57492/8932/4087/2626/22823/8861/57504/672/1655/23186/80816/5926/6760/23429/7703/23269/22936/11016/8819/7421/55696/6426</t>
+          <t>10445/51230/10856/9070/3054/6045/4297/1876/11091/9757/5929/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GO:0000775</t>
+          <t>GO:0099080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chromosome, centromeric region</t>
+          <t>supramolecular complex</t>
         </is>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>0.3351656048405844</v>
+        <v>-0.2727039280104081</v>
       </c>
       <c r="E4">
-        <v>2.297434588922334</v>
+        <v>-2.01699823946486</v>
       </c>
       <c r="F4">
-        <v>0.0007765084629774787</v>
+        <v>0.007398377653571694</v>
       </c>
       <c r="G4">
-        <v>0.02613856251160326</v>
+        <v>0.07734667546915863</v>
       </c>
       <c r="H4">
-        <v>0.02105440275534175</v>
+        <v>0.06725797866883358</v>
       </c>
       <c r="I4">
-        <v>344</v>
+        <v>600</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>tags=67%, list=36%, signal=45%</t>
+          <t>tags=89%, list=62%, signal=35%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25942/196528/9682/6599/23081/6598/11143/51548/10274/92822/10735/6597/5885/8243/2959/546/9126/10951/2146/29117/3297/11335/8467/10664</t>
+          <t>7756/7150/8850/7538/6605/2553/7913/23468/3191/10013/1499/324/3297/29117/5093/64332/6714/23435/9112/2959/8243/3190/26523/6597/92822/6598/54617/4654/6599/196528/25942/7706/1025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GO:1990234</t>
+          <t>GO:0070603</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>transferase complex</t>
+          <t>SWI/SNF superfamily-type complex</t>
         </is>
       </c>
       <c r="C5">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>0.2293853839992284</v>
+        <v>-0.2554767391221578</v>
       </c>
       <c r="E5">
-        <v>2.230363156576064</v>
+        <v>-2.024458466288952</v>
       </c>
       <c r="F5">
-        <v>0.0009091673917079393</v>
+        <v>0.004368951233579065</v>
       </c>
       <c r="G5">
-        <v>0.02613856251160326</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H5">
-        <v>0.02105440275534175</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I5">
-        <v>286</v>
+        <v>593</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>tags=49%, list=30%, signal=38%</t>
+          <t>tags=86%, list=62%, signal=35%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>54880/6872/1025/51341/4149/8535/5929/9757/11091/1876/6908/1024/4297/11143/6045/1027/23135/26147/3054/5925/9070/1387/2962/905/83860/2033/55929/2959/5469/10856/3066/8085/1021/23512/51230/3720/63925/1022/56970/10445</t>
+          <t>9219/29998/55249/8607/6604/9188/5928/6605/7913/53615/6760/57504/8932/57492/8467/29117/10445/23512/57459/3066/10856/64919/10042/9112/53335/54815/55929/5977/5925/6597/65980/6598/8289/54617/6599/196528/7528/3065</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GO:0034708</t>
+          <t>GO:1904949</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>methyltransferase complex</t>
+          <t>ATPase complex</t>
         </is>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>0.3097878869753053</v>
+        <v>-0.2554767391221578</v>
       </c>
       <c r="E6">
-        <v>2.12347984544758</v>
+        <v>-2.024458466288952</v>
       </c>
       <c r="F6">
-        <v>0.003071094422790576</v>
+        <v>0.004368951233579065</v>
       </c>
       <c r="G6">
-        <v>0.04723249777309498</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H6">
-        <v>0.03804539866391175</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I6">
-        <v>313</v>
+        <v>593</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tags=61%, list=32%, signal=43%</t>
+          <t>tags=86%, list=62%, signal=35%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6872/4149/5929/9757/11091/1876/4297/6045/23135/26147/3054/9070/10856/3066/8085/23512/51230/3720/63925/10445/2146/22976</t>
+          <t>9219/29998/55249/8607/6604/9188/5928/6605/7913/53615/6760/57504/8932/57492/8467/29117/10445/23512/57459/3066/10856/64919/10042/9112/53335/54815/55929/5977/5925/6597/65980/6598/8289/54617/6599/196528/7528/3065</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GO:0035097</t>
+          <t>GO:0034708</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>histone methyltransferase complex</t>
+          <t>methyltransferase complex</t>
         </is>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>0.3097878869753053</v>
+        <v>-0.2841857031353661</v>
       </c>
       <c r="E7">
-        <v>2.12347984544758</v>
+        <v>-2.051016497196311</v>
       </c>
       <c r="F7">
-        <v>0.003071094422790576</v>
+        <v>0.005877916189770061</v>
       </c>
       <c r="G7">
-        <v>0.04723249777309498</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H7">
-        <v>0.03804539866391175</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>tags=61%, list=32%, signal=43%</t>
+          <t>tags=61%, list=33%, signal=43%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6872/4149/5929/9757/11091/1876/4297/6045/23135/26147/3054/9070/10856/3066/8085/23512/51230/3720/63925/10445/2146/22976</t>
+          <t>22976/2146/10445/63925/3720/51230/23512/8085/3066/10856/9070/3054/26147/23135/6045/4297/1876/11091/9757/5929/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GO:0044665</t>
+          <t>GO:0035097</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MLL1/2 complex</t>
+          <t>histone methyltransferase complex</t>
         </is>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>0.410227237185435</v>
+        <v>-0.2841857031353661</v>
       </c>
       <c r="E8">
-        <v>2.085886809980986</v>
+        <v>-2.051016497196311</v>
       </c>
       <c r="F8">
-        <v>0.002586487445265768</v>
+        <v>0.005877916189770061</v>
       </c>
       <c r="G8">
-        <v>0.04723249777309498</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H8">
-        <v>0.03804539866391175</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I8">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>tags=68%, list=30%, signal=49%</t>
+          <t>tags=61%, list=33%, signal=43%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6872/4149/5929/9757/11091/1876/4297/6045/3054/9070/10856/51230/10445</t>
+          <t>22976/2146/10445/63925/3720/51230/23512/8085/3066/10856/9070/3054/26147/23135/6045/4297/1876/11091/9757/5929/4149/6872</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO:0099080</t>
+          <t>GO:1990234</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>supramolecular complex</t>
+          <t>transferase complex</t>
         </is>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D9">
-        <v>0.2897599924252902</v>
+        <v>-0.1999975176139968</v>
       </c>
       <c r="E9">
-        <v>2.026211313190086</v>
+        <v>-2.121476992659138</v>
       </c>
       <c r="F9">
-        <v>0.00485444201486901</v>
+        <v>0.003524882048770449</v>
       </c>
       <c r="G9">
-        <v>0.05075098470090329</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H9">
-        <v>0.04087951170416008</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I9">
-        <v>522</v>
+        <v>287</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>tags=81%, list=54%, signal=39%</t>
+          <t>tags=49%, list=30%, signal=38%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1025/7706/25942/196528/6599/4654/54617/6598/92822/6597/26523/3190/8243/2959/9112/23435/6714/64332/5093/29117/3297/324/1499/10013/3191/23468/7913/2553/6605/7538</t>
+          <t>10445/56970/1022/63925/3720/51230/23512/1021/8085/3066/10856/5469/2959/55929/2033/83860/905/2962/1387/9070/5925/3054/26147/23135/1027/6045/11143/4297/1024/6908/1876/11091/9757/5929/8535/4149/51341/1025/6872/54880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:0000791</t>
+          <t>GO:0140513</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>euchromatin</t>
+          <t>nuclear protein-containing complex</t>
         </is>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>287</v>
       </c>
       <c r="D10">
-        <v>0.3576094477938627</v>
+        <v>-0.1247859333879007</v>
       </c>
       <c r="E10">
-        <v>2.0048221168274</v>
+        <v>-2.204506191682019</v>
       </c>
       <c r="F10">
-        <v>0.003285738975519651</v>
+        <v>0.001374587986442749</v>
       </c>
       <c r="G10">
-        <v>0.04723249777309498</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H10">
-        <v>0.03804539866391175</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I10">
-        <v>222</v>
+        <v>407</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>tags=57%, list=23%, signal=45%</t>
+          <t>tags=52%, list=42%, signal=43%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8805/1385/6667/6908/4654/3091/3725/6045/9070/27125/9314/6929/10856</t>
+          <t>6426/55696/7421/8819/11016/22936/23269/7703/23429/6760/5926/80816/23186/1655/672/57504/8861/22823/2626/4087/8932/57492/10155/196/79718/4089/4094/8467/221037/55120/2309/4780/22976/11335/1050/29117/2146/5468/4802/10445/56970/5970/1022/63925/81608/4801/3720/51230/5451/6932/23512/4090/571/4760/57459/6256/51497/4800/8085/3066/5914/10856/7764/5469/64919/25836/10042/9112/6938/53335/54815/84844/6929/466/2959/5994/55929/1390/4778/5977/6934/55726/3727/83860/10589/27125/3190/905/2962/9070/4602/55818/5925/4086/3054/6597/26147/23135/6774/132660/467/7469/9441/6772/65980/6045/54973/4609/11143/6598/6829/4841/1874/4297/3725/405/4790/1024/3091/8289/54617/1052/6908/4601/1876/4605/7936/7029/4088/11091/865/6599/9757/5929/861/8535/1385/1869/10614/196528/7528/3183/25942/3065/4149/51341/1025/6872/54880</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO:0070603</t>
+          <t>GO:0000775</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SWI/SNF superfamily-type complex</t>
+          <t>chromosome, centromeric region</t>
         </is>
       </c>
       <c r="C11">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D11">
-        <v>0.2669588407538647</v>
+        <v>-0.3073793413913595</v>
       </c>
       <c r="E11">
-        <v>2.002809588189129</v>
+        <v>-2.218408924641497</v>
       </c>
       <c r="F11">
-        <v>0.004146687684102807</v>
+        <v>0.002133366743201307</v>
       </c>
       <c r="G11">
-        <v>0.04768690836718228</v>
+        <v>0.07229567349453091</v>
       </c>
       <c r="H11">
-        <v>0.03841142275800495</v>
+        <v>0.06286580303872254</v>
       </c>
       <c r="I11">
-        <v>592</v>
+        <v>345</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>tags=86%, list=61%, signal=35%</t>
+          <t>tags=67%, list=36%, signal=44%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3065/7528/196528/6599/54617/8289/6598/65980/6597/5925/5977/55929/54815/53335/9112/10042/64919/10856/3066/57459/23512/10445/29117/8467/57492/8932/57504/6760/53615/7913/6605/5928/9188/6604/8607/55249/29998/9219</t>
+          <t>10664/8467/11335/3297/29117/2146/10951/9126/546/2959/8243/5885/6597/10735/92822/10274/51548/11143/6598/23081/6599/9682/196528/25942</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO:1904949</t>
+          <t>GO:1902494</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATPase complex</t>
+          <t>catalytic complex</t>
         </is>
       </c>
       <c r="C12">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="D12">
-        <v>0.2669588407538647</v>
+        <v>-0.1898163918062701</v>
       </c>
       <c r="E12">
-        <v>2.002809588189129</v>
+        <v>-2.60561578885221</v>
       </c>
       <c r="F12">
-        <v>0.004146687684102807</v>
+        <v>0.0002479856035655127</v>
       </c>
       <c r="G12">
-        <v>0.04768690836718228</v>
+        <v>0.02851834441003396</v>
       </c>
       <c r="H12">
-        <v>0.03841142275800495</v>
+        <v>0.02479856035655127</v>
       </c>
       <c r="I12">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>tags=86%, list=61%, signal=35%</t>
+          <t>tags=78%, list=62%, signal=36%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3065/7528/196528/6599/54617/8289/6598/65980/6597/5925/5977/55929/54815/53335/9112/10042/64919/10856/3066/57459/23512/10445/29117/8467/57492/8932/57504/6760/53615/7913/6605/5928/9188/6604/8607/55249/29998/9219</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GO:0071339</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MLL1 complex</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>18</v>
-      </c>
-      <c r="D13">
-        <v>0.3921949083728705</v>
-      </c>
-      <c r="E13">
-        <v>1.941948547743931</v>
-      </c>
-      <c r="F13">
-        <v>0.01016926146288999</v>
-      </c>
-      <c r="G13">
-        <v>0.08582599169001748</v>
-      </c>
-      <c r="H13">
-        <v>0.06913214891278298</v>
-      </c>
-      <c r="I13">
-        <v>286</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>tags=67%, list=30%, signal=48%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>6872/4149/5929/11091/1876/4297/6045/3054/9070/10856/51230/10445</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GO:0000793</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>condensed chromosome</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>0.2905755423275605</v>
-      </c>
-      <c r="E14">
-        <v>1.895215168233888</v>
-      </c>
-      <c r="F14">
-        <v>0.01375866671145972</v>
-      </c>
-      <c r="G14">
-        <v>0.08944418726311376</v>
-      </c>
-      <c r="H14">
-        <v>0.07204657646822894</v>
-      </c>
-      <c r="I14">
-        <v>374</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>tags=66%, list=39%, signal=42%</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3146/25942/196528/6599/29781/6598/92822/6597/5885/8243/2959/546/23476/9126/29117/3297/11335/8467/10664/324/672</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GO:0000785</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>chromatin</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>476</v>
-      </c>
-      <c r="D15">
-        <v>0.1117541535442239</v>
-      </c>
-      <c r="E15">
-        <v>1.863332940803764</v>
-      </c>
-      <c r="F15">
-        <v>0.00795623780968102</v>
-      </c>
-      <c r="G15">
-        <v>0.07624727900944311</v>
-      </c>
-      <c r="H15">
-        <v>0.06141657256595875</v>
-      </c>
-      <c r="I15">
-        <v>361</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>tags=42%, list=37%, signal=52%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>6872/4613/2078/4149/10765/3065/25942/3183/7528/196528/8805/9682/1869/6097/1997/6046/1385/861/687/6599/1958/23081/11091/4088/7029/7936/6668/3110/1876/4601/6667/7022/6908/4654/2113/1052/54617/8289/3091/10919/2313/4790/405/6909/11278/3725/7543/6671/1874/7004/688/6598/11143/23028/2551/4609/79923/4901/2308/6045/65980/6772/8019/51548/467/10274/7071/389058/8626/10735/28999/10691/3200/6774/2625/10215/6597/7030/3054/4086/5925/55818/9070/1316/1387/1106/221937/5885/3190/51274/9889/27125/8553/6935/2115/3170/9324/10661/7544/3727/6934/5079/27086/121340/2033/5977/4778/1390/55929/2100/9314/466/6929/54815/53335/6938/10725/9112/10042/25836/3659/3169/64919/10608/5241/5469/546/2908/10856/5914/3066/93649/4800/6256/23435/84913/3516/57459/4205/4760/64344/571/23476/64843/4090/23512/4335/6932/5451/51230/3720/4801/9126/7020/93986/5970/11279/56970/10445/4802/3087/4209/10951/367/5468/2146/6670/29117/26959/56980/3297/23030/1050/11335/4780/2309/55120/3215/3662/221037/1105/1998/116113/8467/9839/7182/4094/7552/4089/6688/83855/84619/196/3172/10155/2627/57492/8932/4087/2626/6928/10481</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GO:0016514</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SWI/SNF complex</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>17</v>
-      </c>
-      <c r="D16">
-        <v>0.3836864891126643</v>
-      </c>
-      <c r="E16">
-        <v>1.857837886772473</v>
-      </c>
-      <c r="F16">
-        <v>0.01044838159704561</v>
-      </c>
-      <c r="G16">
-        <v>0.08582599169001748</v>
-      </c>
-      <c r="H16">
-        <v>0.06913214891278298</v>
-      </c>
-      <c r="I16">
-        <v>215</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>tags=59%, list=22%, signal=47%</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>196528/6599/8289/6598/65980/6597/5925/5977/53335/64919</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GO:0005789</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>endoplasmic reticulum membrane</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>-0.431835072275344</v>
-      </c>
-      <c r="E17">
-        <v>-1.746673505903897</v>
-      </c>
-      <c r="F17">
-        <v>0.01477773528694923</v>
-      </c>
-      <c r="G17">
-        <v>0.08944418726311376</v>
-      </c>
-      <c r="H17">
-        <v>0.07204657646822894</v>
-      </c>
-      <c r="I17">
-        <v>372</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>tags=82%, list=39%, signal=51%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>7494/90993/253782/6721/972/6720/10113/10488/4854</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GO:0031984</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>organelle subcompartment</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>11</v>
-      </c>
-      <c r="D18">
-        <v>-0.431835072275344</v>
-      </c>
-      <c r="E18">
-        <v>-1.746673505903897</v>
-      </c>
-      <c r="F18">
-        <v>0.01477773528694923</v>
-      </c>
-      <c r="G18">
-        <v>0.08944418726311376</v>
-      </c>
-      <c r="H18">
-        <v>0.07204657646822894</v>
-      </c>
-      <c r="I18">
-        <v>372</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>tags=82%, list=39%, signal=51%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>7494/90993/253782/6721/972/6720/10113/10488/4854</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GO:0042175</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nuclear outer membrane-endoplasmic reticulum membrane network</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>11</v>
-      </c>
-      <c r="D19">
-        <v>-0.431835072275344</v>
-      </c>
-      <c r="E19">
-        <v>-1.746673505903897</v>
-      </c>
-      <c r="F19">
-        <v>0.01477773528694923</v>
-      </c>
-      <c r="G19">
-        <v>0.08944418726311376</v>
-      </c>
-      <c r="H19">
-        <v>0.07204657646822894</v>
-      </c>
-      <c r="I19">
-        <v>372</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>tags=82%, list=39%, signal=51%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>7494/90993/253782/6721/972/6720/10113/10488/4854</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GO:0098827</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>endoplasmic reticulum subcompartment</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>11</v>
-      </c>
-      <c r="D20">
-        <v>-0.431835072275344</v>
-      </c>
-      <c r="E20">
-        <v>-1.746673505903897</v>
-      </c>
-      <c r="F20">
-        <v>0.01477773528694923</v>
-      </c>
-      <c r="G20">
-        <v>0.08944418726311376</v>
-      </c>
-      <c r="H20">
-        <v>0.07204657646822894</v>
-      </c>
-      <c r="I20">
-        <v>372</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>tags=82%, list=39%, signal=51%</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>7494/90993/253782/6721/972/6720/10113/10488/4854</t>
+          <t>9219/29998/55249/8607/8473/5591/8850/6604/57680/1457/9188/58508/5928/51317/3187/6605/2145/7307/4221/7913/23468/7520/54623/10013/23492/84759/6907/23309/1499/9611/2122/53615/6426/55696/8819/23269/7703/6760/5926/23186/1655/672/57504/324/22823/8932/57492/79718/8467/221037/22976/29117/2146/10445/56970/1022/63925/3720/51230/23512/57459/1021/8085/3066/10856/7764/5469/64919/10042/9112/53335/54815/2959/55929/5977/2033/83860/3190/26523/905/2962/1387/9070/55818/5925/3054/6597/26147/23135/1027/65980/6045/23028/11143/6598/4297/1024/8289/54617/6908/1876/11091/6599/9757/5929/8535/196528/7528/3183/25942/3065/4149/51341/1025/6872/54880</t>
         </is>
       </c>
     </row>
